--- a/out/policy_events_2026-06-09.xlsx
+++ b/out/policy_events_2026-06-09.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,22 +508,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>증권가 9곳 "지금 사라"…현대, 관세 7조 족쇄 끊고 미국서 직접 만든다 - 글로벌이코노믹</t>
+          <t>美 '301조' 이어 EU '50% 관세 폭탄' … 李정부, 거센 통상 파고 시험대 - 뉴데일리</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>증권가 9곳 "지금 사라"…현대, 관세 7조 족쇄 끊고 미국서 직접 만든다&amp;nbsp;&amp;nbsp;글로벌이코노믹</t>
+          <t>美 '301조' 이어 EU '50% 관세 폭탄' … 李정부, 거센 통상 파고 시험대&amp;nbsp;&amp;nbsp;뉴데일리</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Mon, 08 Jun 2026 20:41:26 GMT</t>
+          <t>Mon, 08 Jun 2026 01:18:44 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNUC1VQm5nakdncWRId0FLM3pWZF9zckRQcVdpcngzb3lRS2xST2NDdXNzSVRGZTZxVGtWTlNDOEgzUDhZYnF5cWcyQ21qWG9iZkpnVTdDYkZGQlFIanlLNkNxWGVQTDdWdFctZWJrS0dKRmFITFNTT1dNYmpTbDdXNVZ1cWE4M2Ra?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE1jM2E2X0tHUjNNd1BGb3VGMlJkN1hMMXowLThld2p2cDE4TEtlaC03Q0NZOGRiRFNpM2VpYzRnZTRFS05hQ2JXRmFTZ1c5blV5Rldnb0xIOTIzMVM4QkwxZ3d1elAzWHlIeEhYRHlQQXota2lHd2d2M1ZTUdIBgAFBVV95cUxQUFE0WEljd1pRdC1wX2o4ejlWdDdxd1pGZ2JJTGZwUmlkcjQxWUNMNGktdFFQbXFId0cyRFJDaWZYa3pkemp1ZHFIdUVwZW43WWxOZXFIVDlRdEpGLXpMLU42NDhVTE1waGNtWmFLWnBpOGlaM2NaaUllb3JhUVl4aw?oc=5</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -545,22 +545,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[구리 가격] 재고 감소·美 관세 변수에 상승…비철금속은 보합권 - 산업일보</t>
+          <t>美 CNBC "中 전기차, 관세장벽에도 수년 내 美 시장 진출할 것" By The Guru - Investing.com 한국어</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[구리 가격] 재고 감소·美 관세 변수에 상승…비철금속은 보합권&amp;nbsp;&amp;nbsp;산업일보</t>
+          <t>美 CNBC "中 전기차, 관세장벽에도 수년 내 美 시장 진출할 것" By The Guru&amp;nbsp;&amp;nbsp;Investing.com 한국어</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Mon, 08 Jun 2026 21:52:28 GMT</t>
+          <t>Mon, 08 Jun 2026 06:26:00 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiSEFVX3lxTFBHbFVGY3RBYk5JZjFITUNoazNFWTk2YUtZcVlxS2NlWXRlVjFDRDl2SnI1NTF5V1JfZU1aMnRjOWYxU1RCdzRZaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5idnlFVnVINnN6Z05JUjRZNmZtaEtkNVhkdGVCMWVTZTFvWTdyTE5CVEE3T3dJU3c3RXVkTFczeEdHZEhDNjdTSC00ZFNWR1c1UzJwUlU3aXpwZnVyckpPdXFyck95cXRFVmlaOV9kUHk?oc=5</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -570,7 +570,7 @@
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -582,22 +582,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>미 50% 고율 관세 1년, EU 대미 수출 34% 급감 - 스틸데일리</t>
+          <t>증권가 9곳 "지금 사라"…현대, 관세 7조 족쇄 끊고 미국서 직접 만든다 - 글로벌이코노믹</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>미 50% 고율 관세 1년, EU 대미 수출 34% 급감&amp;nbsp;&amp;nbsp;스틸데일리</t>
+          <t>증권가 9곳 "지금 사라"…현대, 관세 7조 족쇄 끊고 미국서 직접 만든다&amp;nbsp;&amp;nbsp;글로벌이코노믹</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mon, 08 Jun 2026 21:00:00 GMT</t>
+          <t>Mon, 08 Jun 2026 20:41:26 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE54THBEaC1NRDlRUWt4Wk5nREtUOEs0c0E4MWxqQy04OWhrbGw1UXhXOUVZNkhWOGJLQnFuUlRaUUJpaWxXc3VQVHd0NEt4azFaY2dTem9IZHk2Y3V2MktxNERqcnZfTnBuc2phUDg5b03SAXRBVV95cUxQbXNRdlVlR0VQczRuWWRvX2FnVmUxZG1OZUZnaFptZEVDX0NnV2JtcEJCZGl6UDJDUmlEaDlQN1A4U25qZndpMG1najZCTklPVnh5Z3dSLVpWSnZmY21OTVI1RGpkWWNvVVJJa2drc3JGUHhOSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxNUC1VQm5nakdncWRId0FLM3pWZF9zckRQcVdpcngzb3lRS2xST2NDdXNzSVRGZTZxVGtWTlNDOEgzUDhZYnF5cWcyQ21qWG9iZkpnVTdDYkZGQlFIanlLNkNxWGVQTDdWdFctZWJrS0dKRmFITFNTT1dNYmpTbDdXNVZ1cWE4M2Ra?oc=5</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -619,32 +619,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>인도, 미국에 무역협정 우대 관세 요구 - Investing.com 한국어</t>
+          <t>트럼프 “반도체 관세 100%”…삼성·SK하이닉스 직격탄인가? - MSN</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>인도, 미국에 무역협정 우대 관세 요구&amp;nbsp;&amp;nbsp;Investing.com 한국어</t>
+          <t>트럼프 “반도체 관세 100%”…삼성·SK하이닉스 직격탄인가?&amp;nbsp;&amp;nbsp;MSN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Mon, 08 Jun 2026 14:07:00 GMT</t>
+          <t>Mon, 08 Jun 2026 21:30:27 GMT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBsTXlBMkFaMlJ3dndyOHNuem5lWTJaaUlHMDJzVlB2d3VTaTZtZy1WVUVQd3dNTHItNmJDdUNabjA1bWM1QW5CWHpqUEFXcGhkVUNySnM5MnFRcTNMY0hmTWd2bl9pMTNNdGtsOTM5SFk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AJBVV95cUxPbUFISkNhYTNUOW9sZmN5Zk5GOWo3WDhDSV9HUnVRUFFPbVp1Ti1jMTlndHRNeGc3dWJFZlJ5RVJWUy14N25KVmFaS2JjR3VsQkM3UXRYbC1KVWJaaDkxQUhiZmpBdnpWWXNfQl82bXFXUTJob0RnZkktM3REREx6VGF4cVE2OGdvQnhWbkVYcGpET0ZhakdzNjBldjVIcXRtNEtNVkNjaGlRUS1CVm9xYTNOODEtUkZhMnAxLTRsbUtBVVRUdWlNLXU4aF93OGw2d1B5MFAzdGsxSERlZlJvWjZJb1J4YlNSb2lHMzJxU3NhdjdQVTBrOFpBOFRjeVE3Sjc4LWZGNHJTc2ZqNklEMGtBZlNabXItV3RvcXRxZzN6ekVhN3dWT3BTaVRaUWJQcUpvQ0h5MmdrU1hyOEMwMDVTSDYwLWc5RGM2dEpmOUc?oc=5</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I6" t="inlineStr"/>
     </row>
@@ -656,22 +656,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>美 CNBC "中 전기차, 관세장벽에도 수년 내 美 시장 진출할 것" - 더구루</t>
+          <t>K-철강, EU 관세 장벽에 제동…美 AI 데이터센터로 파고 넘는다 - 매일일보</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>美 CNBC "中 전기차, 관세장벽에도 수년 내 美 시장 진출할 것"&amp;nbsp;&amp;nbsp;더구루</t>
+          <t>K-철강, EU 관세 장벽에 제동…美 AI 데이터센터로 파고 넘는다&amp;nbsp;&amp;nbsp;매일일보</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mon, 08 Jun 2026 05:19:43 GMT</t>
+          <t>Mon, 08 Jun 2026 05:08:37 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTE8zcGJWQmdoU2VoVHVBZDdBdVB4ZGgtbUQ1UkVFOWdrME5leVRfV3prZE5saHZOV2h6cXA5VlNpRG5tTEdLaGNwd1dBeW5zMXZ5ZmFidDJWdVZZellWTk9JR05uUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE43cFMwZFFKVWJHMkNmaVp1RDVSUlNaa1lRN2o1MEZZazZ1TEc4Q3NYX05Hcnk3NElNWnlyVmhCTXVLZVg0eFpJdVo1d2kwci1qVHlaMjFkdXlxZFdEQ1ZsQWV0S0c?oc=5</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -693,22 +693,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>관세국경인재개발원, X-ray 판독 교육훈련 고도화에 박차 - intn.co.kr</t>
+          <t>LG엔솔, 물꼬 텄다…삼성·SK도 美 관세 환급 검토 - 서울경제TV</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>관세국경인재개발원, X-ray 판독 교육훈련 고도화에 박차&amp;nbsp;&amp;nbsp;intn.co.kr</t>
+          <t>LG엔솔, 물꼬 텄다…삼성·SK도 美 관세 환급 검토&amp;nbsp;&amp;nbsp;서울경제TV</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mon, 08 Jun 2026 01:03:47 GMT</t>
+          <t>Mon, 08 Jun 2026 09:26:13 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE9ZRWNKdHBGUWFmaDd2dHRCcGJlUDZyd0VQaEhkejloNVplMWtmOEo0Q0pDWU1mSTg0TTRyQV8zZ01NUDVhY2RkREZxZlNBNTctY3NGZ3FndWpxTU11cklaMUJTaXNfU0djcGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE94S21vY2xwTlc2ZDZNUDMtWEY2dHhmLVMzNjZEM25oa3pYYmZnR2g5VkFGcV9yU0tVVkl1a0tXRFV2VlVRZGN3YVVoMTAtcUhwNEhZTjRPdlJ4ZWxFcWExcVJQVUQ?oc=5</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -730,22 +730,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>이란 전쟁에 관세 폭탄까지… 中 초저가 직구 플랫폼 ‘초성장 시대’ 끝났다 - 글로벌이코노믹</t>
+          <t>관세국경인재개발원, X-ray 판독 고도화 박차 - 네이트</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>이란 전쟁에 관세 폭탄까지… 中 초저가 직구 플랫폼 ‘초성장 시대’ 끝났다&amp;nbsp;&amp;nbsp;글로벌이코노믹</t>
+          <t>관세국경인재개발원, X-ray 판독 고도화 박차&amp;nbsp;&amp;nbsp;네이트</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mon, 08 Jun 2026 20:50:00 GMT</t>
+          <t>Mon, 08 Jun 2026 01:27:00 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPSHZLYXJOM2VWcTBDX28wa0g4M1lrRVQxT050T3gzOTJmN0lKbDAzRzhsMVFyMThXOVZWeUl6ZkQ3eEdYcXg1QUlobzYzR18tMDdfU0Q1SDUtSG11Y0VRM0RvZUZnVE1uZkZFVllyZGtqVmxrQ21GeUJhcWJ5ckQzZUFBLUJNWnlT?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE9seDE5azdtX0l2eDVRMU9tRmVPRjlSa3BEdnZ6VFVjakVOYTBRd2trcnFkTEt5RWpGdEpQeTlYQnRMWXZoWmVRem9xLWgxajVuSjJJ?oc=5</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I9" t="inlineStr"/>
     </row>
@@ -767,22 +767,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>모건 스탠리: 미국 구리 관세 결정, 핵심 위험 요인으로 지목 - Investing.com 한국어</t>
+          <t>[구리 가격] 재고 감소·美 관세 변수에 상승…비철금속은 보합권 - 산업일보</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>모건 스탠리: 미국 구리 관세 결정, 핵심 위험 요인으로 지목&amp;nbsp;&amp;nbsp;Investing.com 한국어</t>
+          <t>[구리 가격] 재고 감소·美 관세 변수에 상승…비철금속은 보합권&amp;nbsp;&amp;nbsp;산업일보</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mon, 08 Jun 2026 08:58:00 GMT</t>
+          <t>Mon, 08 Jun 2026 21:52:28 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE5mRkpLNmFZbkhPX3U3b3JlN3J1ek9DUWF3VnBwb0F4MnNRQU5wd1hqME9xMl94d2huVHMyejF2XzBYWEhfRnY4ZEpzckFMc0ljOGlGbmlNWDRLcEtudEljQ19PWVF4bFhyemhoX1dBRG1nNklWZTdz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiSEFVX3lxTFBHbFVGY3RBYk5JZjFITUNoazNFWTk2YUtZcVlxS2NlWXRlVjFDRDl2SnI1NTF5V1JfZU1aMnRjOWYxU1RCdzRZaw?oc=5</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -804,22 +804,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LG엔솔 1000억 환급…K배터리 ‘관세 청구서’ 되돌아온다 - 글로벌이코노믹</t>
+          <t>미 50% 고율 관세 1년, EU 대미 수출 34% 급감 - 스틸데일리</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LG엔솔 1000억 환급…K배터리 ‘관세 청구서’ 되돌아온다&amp;nbsp;&amp;nbsp;글로벌이코노믹</t>
+          <t>미 50% 고율 관세 1년, EU 대미 수출 34% 급감&amp;nbsp;&amp;nbsp;스틸데일리</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Mon, 08 Jun 2026 00:01:16 GMT</t>
+          <t>Mon, 08 Jun 2026 21:00:00 GMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxQeVdPSVBwcGFlcmx6UHA1b0VSVWg4RzNRWThrNUpINnRtLVRWbTMwaFBleVdVei1zaHV2NHVYQllCUmhueng3LWh4MWpzOElCRlU2aDY4c2NZeG5UQU84VC1nbzZjekpSdW56cVlxNUN1eEQxc1A1WmlhTk1KXzhMVkQzUUFlZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE54THBEaC1NRDlRUWt4Wk5nREtUOEs0c0E4MWxqQy04OWhrbGw1UXhXOUVZNkhWOGJLQnFuUlRaUUJpaWxXc3VQVHd0NEt4azFaY2dTem9IZHk2Y3V2MktxNERqcnZfTnBuc2phUDg5b03SAXRBVV95cUxQbXNRdlVlR0VQczRuWWRvX2FnVmUxZG1OZUZnaFptZEVDX0NnV2JtcEJCZGl6UDJDUmlEaDlQN1A4U25qZndpMG1najZCTklPVnh5Z3dSLVpWSnZmY21OTVI1RGpkWWNvVVJJa2drc3JGUHhOSQ?oc=5</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -841,32 +841,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>美 '강제노동' 12.5% 관세 예고… 소비재 수출 '15% 방어선' 시험대 - 중소기업신문</t>
+          <t>인도, 미국에 무역협정 우대 관세 요구 - Investing.com 한국어</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>美 '강제노동' 12.5% 관세 예고… 소비재 수출 '15% 방어선' 시험대&amp;nbsp;&amp;nbsp;중소기업신문</t>
+          <t>인도, 미국에 무역협정 우대 관세 요구&amp;nbsp;&amp;nbsp;Investing.com 한국어</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Mon, 08 Jun 2026 01:51:12 GMT</t>
+          <t>Mon, 08 Jun 2026 14:07:00 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE85bEFDcmdCYWMyNkJxYnUwN1JwMjRYU1JpOF9obnRlTlRDQ0RYVXE3VlR1UHpjc3ZaZ2FPWExkVXREcVB0MnJwbWtsUzZxM1NNQldsN2lVQy1nU18yc190d3I0UGRDTnJUTWR3NA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBsTXlBMkFaMlJ3dndyOHNuem5lWTJaaUlHMDJzVlB2d3VTaTZtZy1WVUVQd3dNTHItNmJDdUNabjA1bWM1QW5CWHpqUEFXcGhkVUNySnM5MnFRcTNMY0hmTWd2bl9pMTNNdGtsOTM5SFk?oc=5</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I12" t="inlineStr"/>
     </row>
@@ -878,22 +878,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LG에너지솔루션, 美관세 환급 신청…1000억 이상 현금 유입 기대 - 이지경제</t>
+          <t>美 CNBC "中 전기차, 관세장벽에도 수년 내 美 시장 진출할 것" - 더구루</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LG에너지솔루션, 美관세 환급 신청…1000억 이상 현금 유입 기대&amp;nbsp;&amp;nbsp;이지경제</t>
+          <t>美 CNBC "中 전기차, 관세장벽에도 수년 내 美 시장 진출할 것"&amp;nbsp;&amp;nbsp;더구루</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Mon, 08 Jun 2026 04:59:04 GMT</t>
+          <t>Mon, 08 Jun 2026 05:19:43 GMT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE91RlRFMlQ2c0VFRXN2R2NDUEhnRWx0R1ZhdWRWbEs0OGFLLUdkbEk0dVRrM01faFBtWGU1d01IbDZaalZuTVhsdzRuLTF5aFZKM3ZnT0c4MDhKR2stUEkzT3pyQ3ZfaGNIRi1DYk1B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTE8zcGJWQmdoU2VoVHVBZDdBdVB4ZGgtbUQ1UkVFOWdrME5leVRfV3prZE5saHZOV2h6cXA5VlNpRG5tTEdLaGNwd1dBeW5zMXZ5ZmFidDJWdVZZellWTk9JR05uUQ?oc=5</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -915,22 +915,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LG엔솔, 美 관세 환급 신청…수천억 규모 전망 - v.daum.net</t>
+          <t>관세국경인재개발원, X-ray 판독 교육훈련 고도화에 박차 - intn.co.kr</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LG엔솔, 美 관세 환급 신청…수천억 규모 전망&amp;nbsp;&amp;nbsp;v.daum.net</t>
+          <t>관세국경인재개발원, X-ray 판독 교육훈련 고도화에 박차&amp;nbsp;&amp;nbsp;intn.co.kr</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sun, 07 Jun 2026 23:19:07 GMT</t>
+          <t>Mon, 08 Jun 2026 01:03:47 GMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE5DeDFVUGFueklMNHM0T0VNaU9uX1NUaGtPajctV2xuRVFvMENDZG53eUljdE5URlBOMmN6ek1ueWFJZkotTGkzejgwTTh5Rm8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE9ZRWNKdHBGUWFmaDd2dHRCcGJlUDZyd0VQaEhkejloNVplMWtmOEo0Q0pDWU1mSTg0TTRyQV8zZ01NUDVhY2RkREZxZlNBNTctY3NGZ3FndWpxTU11cklaMUJTaXNfU0djcGc?oc=5</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -940,34 +940,34 @@
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FTA</t>
+          <t>관세</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>한-아세안 자유무역협정(FTA) 개선 제1차 공식협상 개최 - 서울Pn</t>
+          <t>LG엔솔·삼성SDI 튼 美 관세 환급 물꼬…산업계 전반 번지나 [美관세 환급러시] - 이투데이</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>한-아세안 자유무역협정(FTA) 개선 제1차 공식협상 개최&amp;nbsp;&amp;nbsp;서울Pn한-아세안 FTA 개선 위한 1차 공식협상 서울서 개최&amp;nbsp;&amp;nbsp;연합뉴스핵심광물·공급망 협력 강화… 한국·아세안 FTA 손본다&amp;nbsp;&amp;nbsp;문화일보한-아세안 FTA 개선 협상 개시…디지털·핵심광물 협력 강화&amp;nbsp;&amp;nbsp;파이낸셜뉴스韓·아세안 FTA 개선 협상 개시…디지털·공급망 협력 확대 추진&amp;nbsp;&amp;nbsp;아시아경제한-아세안 FTA 개선 1차 공식협상 서울서 개최…공급망 등 13개 분야 진행&amp;nbsp;&amp;nbsp;v.daum.net한·아세안 FTA 개선협상 개최…서울서 12일까지&amp;nbsp;&amp;nbsp;뉴스웍스한·아세안 FTA 첫 개선협상 착수…디지털·공급망 논의&amp;nbsp;&amp;nbsp;더팩트한-아세안 FTA 개선 제1차 공식협상 개최&amp;nbsp;&amp;nbsp;데일리안</t>
+          <t>LG엔솔·삼성SDI 튼 美 관세 환급 물꼬…산업계 전반 번지나 [美관세 환급러시]&amp;nbsp;&amp;nbsp;이투데이</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Mon, 08 Jun 2026 00:02:49 GMT</t>
+          <t>Mon, 08 Jun 2026 07:06:00 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiYkFVX3lxTE5BczMtMVkyU3dxUEtocXczQzVWLWhhR2FCNjZjMUhfYjI1RjY5LTFfUGV3RkZfelVXQkx1LWJSWnJGNVQ3R3hqaXIzU0VtT0VHV1UteGo1RWE4eDJXS1RwTkNB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE9jM3lhRVhRSnphR2E1dVptQzJUOEtmeVM4RnFCRVd6REJOUXEwMjBDNUNES0NPcTVxNHo0bndUZFUzbm9qOGdWbUhEY1pvWkZfdXh6Qw?oc=5</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -984,74 +984,74 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FTA</t>
+          <t>관세</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>경북동부FTA통상진흥센터, 원산지증명 실무교육 실시 - kyongbuk.co.kr</t>
+          <t>이란 전쟁에 관세 폭탄까지… 中 초저가 직구 플랫폼 ‘초성장 시대’ 끝났다 - 글로벌이코노믹</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>경북동부FTA통상진흥센터, 원산지증명 실무교육 실시&amp;nbsp;&amp;nbsp;kyongbuk.co.kr</t>
+          <t>이란 전쟁에 관세 폭탄까지… 中 초저가 직구 플랫폼 ‘초성장 시대’ 끝났다&amp;nbsp;&amp;nbsp;글로벌이코노믹</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Mon, 08 Jun 2026 09:35:42 GMT</t>
+          <t>Mon, 08 Jun 2026 20:50:00 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTFB6ZUUxVmo1SHJiTnNDRmdvWk95RkhkVHZGTFBleGRnM1VRZFVpUXo3a19qLS1XUU5uYm4zdGhncFJYb3EyN0wtX2FsMlZhYzZPckpQS0FlTEJ6dWQwQ3JwcXdPV3RXX1g1Y2VyUEs3NA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPSHZLYXJOM2VWcTBDX28wa0g4M1lrRVQxT050T3gzOTJmN0lKbDAzRzhsMVFyMThXOVZWeUl6ZkQ3eEdYcXg1QUlobzYzR18tMDdfU0Q1SDUtSG11Y0VRM0RvZUZnVE1uZkZFVllyZGtqVmxrQ21GeUJhcWJ5ckQzZUFBLUJNWnlT?oc=5</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FTA</t>
+          <t>관세</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>포항상의, FTA 원산지증명 실무교육 개최…수출기업 통상역량 높인다 - 경북신문</t>
+          <t>모건 스탠리: 미국 구리 관세 결정, 핵심 위험 요인으로 지목 - Investing.com 한국어</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>포항상의, FTA 원산지증명 실무교육 개최…수출기업 통상역량 높인다&amp;nbsp;&amp;nbsp;경북신문</t>
+          <t>모건 스탠리: 미국 구리 관세 결정, 핵심 위험 요인으로 지목&amp;nbsp;&amp;nbsp;Investing.com 한국어</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Mon, 08 Jun 2026 04:42:00 GMT</t>
+          <t>Mon, 08 Jun 2026 08:58:00 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBzZUZzX3dIWTlkNXVkLTl0Y090clBkYnRZOTVnOW1xQ2RaZFFBXzhmYThOMnN4dkU5WlJLTFVNdnYzWmpTY3BUZFQtSXR3TEtOU3ljUThPa0U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE5mRkpLNmFZbkhPX3U3b3JlN3J1ek9DUWF3VnBwb0F4MnNRQU5wd1hqME9xMl94d2huVHMyejF2XzBYWEhfRnY4ZEpzckFMc0ljOGlGbmlNWDRLcEtudEljQ19PWVF4bFhyemhoX1dBRG1nNklWZTdz?oc=5</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I17" t="inlineStr"/>
     </row>
@@ -1063,32 +1063,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>한-아세안 FTA 개선 협상 개시···핵심광물·공급망 협력 강화 - 스틸데일리</t>
+          <t>경북동부FTA통상진흥센터, 원산지증명 실무교육 실시 - kyongbuk.co.kr</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>한-아세안 FTA 개선 협상 개시···핵심광물·공급망 협력 강화&amp;nbsp;&amp;nbsp;스틸데일리</t>
+          <t>경북동부FTA통상진흥센터, 원산지증명 실무교육 실시&amp;nbsp;&amp;nbsp;kyongbuk.co.kr</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Mon, 08 Jun 2026 09:15:00 GMT</t>
+          <t>Mon, 08 Jun 2026 09:35:42 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5MVUNnUkF1QkVocWdLamVnYVV2Y0NZazd6SklkMDc2ZDVXdE90Y0xaRFktSUZ1bHFjdC1TZi1OajZDSGtrZEhqRy1PVHUwMTJ5MW5NSXR0M0lvMC1fcEZiUzRKcDNCNXBNYUFIWnBfOUfSAXRBVV95cUxNdkpHQjBQVmdpTS14TW1maVUtLWFBY0tiV2JLRlFmT25MemFjYmhsdGFPRVloZFhmV2xJSjVYOHJqRHNBRU1LYmpuMkd5Rl9PT0k0U1kyN0E1WW1yUlZjZVp4QUJNMm04NzE5c2szMzdLNW1sUw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTFB6ZUUxVmo1SHJiTnNDRmdvWk95RkhkVHZGTFBleGRnM1VRZFVpUXo3a19qLS1XUU5uYm4zdGhncFJYb3EyN0wtX2FsMlZhYzZPckpQS0FlTEJ6dWQwQ3JwcXdPV3RXX1g1Y2VyUEs3NA?oc=5</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I18" t="inlineStr"/>
     </row>
@@ -1100,32 +1100,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>한-아세안 FTA 개편 시동…디지털·핵심광물 협력 판 키운다 - 에너지신문</t>
+          <t>포항상의, FTA 원산지증명 실무교육 개최…수출기업 통상역량 높인다 - 경북신문</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>한-아세안 FTA 개편 시동…디지털·핵심광물 협력 판 키운다&amp;nbsp;&amp;nbsp;에너지신문</t>
+          <t>포항상의, FTA 원산지증명 실무교육 개최…수출기업 통상역량 높인다&amp;nbsp;&amp;nbsp;경북신문</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Mon, 08 Jun 2026 01:16:19 GMT</t>
+          <t>Mon, 08 Jun 2026 04:42:00 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE0zc19PREcyclRhb1pzTFBYcy05b1M2ZHNUN1lYREpXbzFpZnI1YzFhaXhmNUVnRnR3ellGVnNZLUE1Q0FBQWFFLTM1QzRzdmg4aGtHWG9XX1hxZ2JXNEYwWkltVTUzOVF5RExZcE9UOGZjUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTFBzZUZzX3dIWTlkNXVkLTl0Y090clBkYnRZOTVnOW1xQ2RaZFFBXzhmYThOMnN4dkU5WlJLTFVNdnYzWmpTY3BUZFQtSXR3TEtOU3ljUThPa0U?oc=5</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I19" t="inlineStr"/>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>산업부, '한-아세안 FTA 개선 공식협상'…공급망·핵심광물 집중 - 페로타임즈</t>
+          <t>한-아세안 FTA 개선 협상 개시···핵심광물·공급망 협력 강화 - 스틸데일리</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>산업부, '한-아세안 FTA 개선 공식협상'…공급망·핵심광물 집중&amp;nbsp;&amp;nbsp;페로타임즈</t>
+          <t>한-아세안 FTA 개선 협상 개시···핵심광물·공급망 협력 강화&amp;nbsp;&amp;nbsp;스틸데일리</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Mon, 08 Jun 2026 01:40:00 GMT</t>
+          <t>Mon, 08 Jun 2026 09:15:00 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5yTUstQjlXdi1iUUNkQ20tanhLamJ0VFVsb01IczExZTd4NnB2U2pxSk5XM2NQMV9BSkUxRVNmenl3MXRaMHZhOFMtRzZaVjVUdXJtbVBnSzFFc1RqMHI0WUVncUk5dVE3b0xpeQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5MVUNnUkF1QkVocWdLamVnYVV2Y0NZazd6SklkMDc2ZDVXdE90Y0xaRFktSUZ1bHFjdC1TZi1OajZDSGtrZEhqRy1PVHUwMTJ5MW5NSXR0M0lvMC1fcEZiUzRKcDNCNXBNYUFIWnBfOUfSAXRBVV95cUxNdkpHQjBQVmdpTS14TW1maVUtLWFBY0tiV2JLRlFmT25MemFjYmhsdGFPRVloZFhmV2xJSjVYOHJqRHNBRU1LYmpuMkd5Rl9PT0k0U1kyN0E1WW1yUlZjZVp4QUJNMm04NzE5c2szMzdLNW1sUw?oc=5</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1174,32 +1174,32 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>한-아세안 FTA, AI·전기차 등 미래산업 대응 협상 본격화 - 에너지플랫폼뉴스</t>
+          <t>포항상공회의소 경북동부FTA통상진흥센터, 원산지증명 완전정복 온라인 교육 개최 안내 - 다경뉴스</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>한-아세안 FTA, AI·전기차 등 미래산업 대응 협상 본격화&amp;nbsp;&amp;nbsp;에너지플랫폼뉴스</t>
+          <t>포항상공회의소 경북동부FTA통상진흥센터, 원산지증명 완전정복 온라인 교육 개최 안내&amp;nbsp;&amp;nbsp;다경뉴스</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Mon, 08 Jun 2026 00:40:59 GMT</t>
+          <t>Mon, 08 Jun 2026 07:30:00 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE8zVlYtdjVPYkZQUmtBRThpSEpjRVZPcHBETE1sU1k2Mkh4c1pDZDlab2VxS2VrcHYwUlZOTmduZjRIMldFcDU3YVYxT3NDb2Z1eXBnNWlLTGlmM0NHMl94RkRXXzdwX1VCUVYtd9IBcEFVX3lxTE5NNEdKWUNKX0ZvdkFvVDNOVzg2ZGM2Y2RiWXRhZlZndm5scEJzSmRTdnc4akQxS0hjY19HRFRvdXQ5alBLN2FmcFJIOG9Tbi12WnZEajYteXVKVURpMngyWVB4VXJlX29tSm80RzQxWGI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiREFVX3lxTE9hbVNYNTBVYzZyX2tpcmlkSWRhY3RTOWY5WDZydHVmRHZLUWhvSUFsTUVUQW80S1I0a0Rqc2xsemVJNWRL?oc=5</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I21" t="inlineStr"/>
     </row>
@@ -1211,22 +1211,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>韓·아세안 FTA 개선 위한 1차 공식협상 서울서 열린다 - IT비즈뉴스</t>
+          <t>산업부, '한-아세안 FTA 개선 공식협상'…공급망·핵심광물 집중 - 페로타임즈</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>韓·아세안 FTA 개선 위한 1차 공식협상 서울서 열린다&amp;nbsp;&amp;nbsp;IT비즈뉴스</t>
+          <t>산업부, '한-아세안 FTA 개선 공식협상'…공급망·핵심광물 집중&amp;nbsp;&amp;nbsp;페로타임즈</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Mon, 08 Jun 2026 04:00:00 GMT</t>
+          <t>Mon, 08 Jun 2026 01:40:00 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5ETnV3b2ltck1kME01elRhQmFzNTJxNkhoeEl2VFVkRnQ5VEVKbmVJaldZRWZSS2dZVVlFc0dKWUdVWUlmOHRNM25jTURybFM2SFFjaHNQQTlrM1lNNDZEQWszUnVuRm95Y3lGMg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5yTUstQjlXdi1iUUNkQ20tanhLamJ0VFVsb01IczExZTd4NnB2U2pxSk5XM2NQMV9BSkUxRVNmenl3MXRaMHZhOFMtRzZaVjVUdXJtbVBnSzFFc1RqMHI0WUVncUk5dVE3b0xpeQ?oc=5</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1248,22 +1248,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>한-아세안 FTA 개선협상 본격 착수 - 디지털·핵심광물·공급망 협력 확대 - 한국도시환경헤럴드</t>
+          <t>한-아세안 FTA 개편 시동…디지털·핵심광물 협력 판 키운다 - 에너지신문</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>한-아세안 FTA 개선협상 본격 착수 - 디지털·핵심광물·공급망 협력 확대&amp;nbsp;&amp;nbsp;한국도시환경헤럴드</t>
+          <t>한-아세안 FTA 개편 시동…디지털·핵심광물 협력 판 키운다&amp;nbsp;&amp;nbsp;에너지신문</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Mon, 08 Jun 2026 01:32:50 GMT</t>
+          <t>Mon, 08 Jun 2026 01:16:19 GMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5OSTM2SEhNSUdJdWlMelZRYXZ6WERlVVFabWdaV2xSVW9JMXNab1FxOVNrLXk0ZVBCOXduRjY5TkJ1Tk1qbFd2YjF4eTJYRUVpdXZrdURSOERXZ2Nsd29JcVJvMnI2NXg2S2J0NNIBcEFVX3lxTE5oZUZMdlBOeHMwaDBnT25sc0hEamU4Y1gtcmVQNmx3S0c1NlJ3MXRyWFlGemhBZUw5LUVsR29sbDlnQzZaUGhyRGc2SVhjdEJJRFRGQl9Ha0JQdzBSV3FSTkhlWXJNRUszdlU5R1R4dks?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE0zc19PREcyclRhb1pzTFBYcy05b1M2ZHNUN1lYREpXbzFpZnI1YzFhaXhmNUVnRnR3ellGVnNZLUE1Q0FBQWFFLTM1QzRzdmg4aGtHWG9XX1hxZ2JXNEYwWkltVTUzOVF5RExZcE9UOGZjUQ?oc=5</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I23" t="inlineStr"/>
     </row>
@@ -1285,22 +1285,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>한-아세안 FTA 개선 협상 닷새 간 열려…디지털·핵심광물 등 협력 강화 - BBS불교방송</t>
+          <t>韓·아세안 FTA 개선 위한 1차 공식협상 서울서 열린다 - IT비즈뉴스</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>한-아세안 FTA 개선 협상 닷새 간 열려…디지털·핵심광물 등 협력 강화&amp;nbsp;&amp;nbsp;BBS불교방송</t>
+          <t>韓·아세안 FTA 개선 위한 1차 공식협상 서울서 열린다&amp;nbsp;&amp;nbsp;IT비즈뉴스</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Mon, 08 Jun 2026 00:05:25 GMT</t>
+          <t>Mon, 08 Jun 2026 04:00:00 GMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE9wUm9vQ1Fwb0xCUjc3MFRpSlE2cXBUUGZGeVdIVnROMzRVOExJTDk1V1ZPTTBsbl9XM1RPRm5WcWgyMzlGeTNvVnRWc0c5OHRKRHIwR2pPMGx0bG4xWFNFeXlZM09rT19PWXV3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5ETnV3b2ltck1kME01elRhQmFzNTJxNkhoeEl2VFVkRnQ5VEVKbmVJaldZRWZSS2dZVVlFc0dKWUdVWUlmOHRNM25jTURybFM2SFFjaHNQQTlrM1lNNDZEQWszUnVuRm95Y3lGMg?oc=5</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1322,22 +1322,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>충남경제진흥원, 일본 오사카 시장개척단 참여기업 모집 - 뉴스밴드</t>
+          <t>한-아세안 FTA, AI·전기차 등 미래산업 대응 협상 본격화 - 에너지플랫폼뉴스</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>충남경제진흥원, 일본 오사카 시장개척단 참여기업 모집&amp;nbsp;&amp;nbsp;뉴스밴드</t>
+          <t>한-아세안 FTA, AI·전기차 등 미래산업 대응 협상 본격화&amp;nbsp;&amp;nbsp;에너지플랫폼뉴스</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Mon, 08 Jun 2026 05:33:26 GMT</t>
+          <t>Mon, 08 Jun 2026 00:40:59 GMT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE9NX1RuRXFZRHRhb2dzd3RDd0s2TnF0NlFndFZzb1JGcHRyQjI1enN6UmN4VzhtUU12ZXVJN2R5ZUZXX251T0RWWGo0dkY3SHVCeXZ0TGkwNzFSeVFFWUNLaTlhRW9HZ0JCOUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE8zVlYtdjVPYkZQUmtBRThpSEpjRVZPcHBETE1sU1k2Mkh4c1pDZDlab2VxS2VrcHYwUlZOTmduZjRIMldFcDU3YVYxT3NDb2Z1eXBnNWlLTGlmM0NHMl94RkRXXzdwX1VCUVYtd9IBcEFVX3lxTE5NNEdKWUNKX0ZvdkFvVDNOVzg2ZGM2Y2RiWXRhZlZndm5scEJzSmRTdnc4akQxS0hjY19HRFRvdXQ5alBLN2FmcFJIOG9Tbi12WnZEajYteXVKVURpMngyWVB4VXJlX29tSm80RzQxWGI?oc=5</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I25" t="inlineStr"/>
     </row>
@@ -1359,22 +1359,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>한-아세안 FTA 개선 1차 공식협상 서울서 개최…공급망 등 13개 분야 진행 - 헤럴드경제</t>
+          <t>한-아세안 FTA 개선협상 본격 착수 - 디지털·핵심광물·공급망 협력 확대 - 한국도시환경헤럴드</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>한-아세안 FTA 개선 1차 공식협상 서울서 개최…공급망 등 13개 분야 진행&amp;nbsp;&amp;nbsp;헤럴드경제</t>
+          <t>한-아세안 FTA 개선협상 본격 착수 - 디지털·핵심광물·공급망 협력 확대&amp;nbsp;&amp;nbsp;한국도시환경헤럴드</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Sun, 07 Jun 2026 23:58:36 GMT</t>
+          <t>Mon, 08 Jun 2026 01:32:50 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTFAwTDRoV204ZGdRZVQ5Rm91M2xqdEN5Q3UxYzJJa1ZRbEwtZ0ZJZVhPZHlDVnhyZFU2bVg2ZlVaQTZKMFlzVjY1N2JuZDZ6MHFQZ1kyWUFR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5OSTM2SEhNSUdJdWlMelZRYXZ6WERlVVFabWdaV2xSVW9JMXNab1FxOVNrLXk0ZVBCOXduRjY5TkJ1Tk1qbFd2YjF4eTJYRUVpdXZrdURSOERXZ2Nsd29JcVJvMnI2NXg2S2J0NNIBcEFVX3lxTE5oZUZMdlBOeHMwaDBnT25sc0hEamU4Y1gtcmVQNmx3S0c1NlJ3MXRyWFlGemhBZUw5LUVsR29sbDlnQzZaUGhyRGc2SVhjdEJJRFRGQl9Ha0JQdzBSV3FSTkhlWXJNRUszdlU5R1R4dks?oc=5</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I26" t="inlineStr"/>
     </row>
@@ -1396,22 +1396,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>韓·아세안 FTA 개선 협상 개시…디지털·공급망 협력 확대 추진 - 네이트</t>
+          <t>충남경제진흥원, 일본 오사카 시장개척단 참여기업 모집 - 뉴스밴드</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>韓·아세안 FTA 개선 협상 개시…디지털·공급망 협력 확대 추진&amp;nbsp;&amp;nbsp;네이트</t>
+          <t>충남경제진흥원, 일본 오사카 시장개척단 참여기업 모집&amp;nbsp;&amp;nbsp;뉴스밴드</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Mon, 08 Jun 2026 02:04:00 GMT</t>
+          <t>Mon, 08 Jun 2026 05:33:26 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE9qOG54dkc1ZEh2ZDFueHdmU3RCcHVTdVJGblc2bkJ5amVwOTMxdFB6eTFiSzViWEk5ZzNGdDByQWplNkJyWkxSR1NXWS1LQXlxcmVB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE9NX1RuRXFZRHRhb2dzd3RDd0s2TnF0NlFndFZzb1JGcHRyQjI1enN6UmN4VzhtUU12ZXVJN2R5ZUZXX251T0RWWGo0dkY3SHVCeXZ0TGkwNzFSeVFFWUNLaTlhRW9HZ0JCOUE?oc=5</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1421,34 +1421,34 @@
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>원산지</t>
+          <t>FTA</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>포항상의, 원산지증명 실무역량 강화 교육 개최 - v.daum.net</t>
+          <t>韓·아세안 FTA 개선 협상 개시…디지털·공급망 협력 확대 추진 - 네이트</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>포항상의, 원산지증명 실무역량 강화 교육 개최&amp;nbsp;&amp;nbsp;v.daum.net</t>
+          <t>韓·아세안 FTA 개선 협상 개시…디지털·공급망 협력 확대 추진&amp;nbsp;&amp;nbsp;네이트</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Mon, 08 Jun 2026 04:50:00 GMT</t>
+          <t>Mon, 08 Jun 2026 02:04:00 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE9vUVpTeFgwdzZndWUzeWczQnBzcEJWYVFhRGFIYUVobEY5T0owR2gwYnlFT1g0RXdxamE4T2VzTUgtd1J0MkZ0RXFGdmZPNnM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE9qOG54dkc1ZEh2ZDFueHdmU3RCcHVTdVJGblc2bkJ5amVwOTMxdFB6eTFiSzViWEk5ZzNGdDByQWplNkJyWkxSR1NXWS1LQXlxcmVB?oc=5</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1470,22 +1470,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>농관원, 국내 첫 염소고기 원산지 판별기술 개발...95% 이상 구분 - 푸드투데이</t>
+          <t>포항상의, 원산지증명 실무역량 강화 교육 개최 - v.daum.net</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>농관원, 국내 첫 염소고기 원산지 판별기술 개발...95% 이상 구분&amp;nbsp;&amp;nbsp;푸드투데이</t>
+          <t>포항상의, 원산지증명 실무역량 강화 교육 개최&amp;nbsp;&amp;nbsp;v.daum.net</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Mon, 08 Jun 2026 01:34:43 GMT</t>
+          <t>Mon, 08 Jun 2026 04:50:00 GMT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE5CWFptbzRiY09WV1BOSGhVbFJkZ2J0WkxzTUpSZW5FOUp6WG1IUHpPdUVkVy05WUVOcnA1U3ZJQkxQblMzT2lhaGoxdGFkVk1ncVBUamduVHZlVXV4Mkp1VQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE9vUVpTeFgwdzZndWUzeWczQnBzcEJWYVFhRGFIYUVobEY5T0owR2gwYnlFT1g0RXdxamE4T2VzTUgtd1J0MkZ0RXFGdmZPNnM?oc=5</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1507,22 +1507,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>포항상의, 원산지증명 실무역량 강화 교육 - hidomin.com</t>
+          <t>농관원, 국내 첫 염소고기 원산지 판별기술 개발...95% 이상 구분 - 푸드투데이</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>포항상의, 원산지증명 실무역량 강화 교육&amp;nbsp;&amp;nbsp;hidomin.com</t>
+          <t>농관원, 국내 첫 염소고기 원산지 판별기술 개발...95% 이상 구분&amp;nbsp;&amp;nbsp;푸드투데이</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Mon, 08 Jun 2026 05:58:00 GMT</t>
+          <t>Mon, 08 Jun 2026 01:34:43 GMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE1yM25ZbVE5YjlETk9uWDRVWlJMMG44Vy1IbXlpUzRpX0ZWOG1wTkdWOVZrNk5wa1pvV2M1dThYWGxCSmpqcThOVlZhYUZxSktQdHFpY1VGeUl1TGRyWjZINmRaWnAybjZOMlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE1HM2wxMEVrM3g4czlXOC1DNWgyemFvdm9BMkhlYmdKaktBZHNEaXpuRDZ4bFFVY3FmOHFubU8wTzdvS0dZaXpzVlNGMkZ4UnBRTFcyeVRLS2lIZXU5ZkpYN3BkY25uTmdq?oc=5</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1544,32 +1544,32 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>포항상의, 원산지증명 실무역량 강화 교육 - 경상매일신문</t>
+          <t>관세청, 원산지증명 발급절차 개선… FTA 활용 지원 확대 - 한국관세신문</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>포항상의, 원산지증명 실무역량 강화 교육&amp;nbsp;&amp;nbsp;경상매일신문</t>
+          <t>관세청, 원산지증명 발급절차 개선… FTA 활용 지원 확대&amp;nbsp;&amp;nbsp;한국관세신문</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Mon, 08 Jun 2026 11:09:36 GMT</t>
+          <t>Mon, 08 Jun 2026 09:06:58 GMT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE5BN1ljM3U2X20tQlRXbkgxTzB6ZXc0Q0IxMDdXNEYydDFNbUJVWjk2R05lTGFaLS11MmtzbENYWXVBU241aFNDYVBGUUt2cDVfclVKX1ZlbUZ0Q0JkYmpB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE12bjhncGV5d2daM0k2V18ySGJ0RjFUUmxzS1dkM2x6UGtTQzROSTdtcGRhZndJdjhodFRkTi1tVFdxbkU5MFhBbHphdG4xNTdxSlJxTUZpbkZmVFJ4UDc4NGtCOTVzTlZGWndF0gFrQVVfeXFMTXZuOGdwZXl3Z1ozSTZXXzJIYnRGMVRSbHNLV2QzbHpQa1NDNE5JN21wZGFmd0l2OGh0VGROLW1UV3FuRTkwWEFsemF0bjE1N3FKUnFNRmluRmZUUnhQNzg0a0I5NXNOVkZad0U?oc=5</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I31" t="inlineStr"/>
     </row>
@@ -1581,32 +1581,32 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>관세청, 원산지증명 발급절차 개선… FTA 활용 지원 확대 - 한국관세신문</t>
+          <t>염소고기 원산지 'DNA·동위원소'로 판별한다 - 세이프타임즈</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>관세청, 원산지증명 발급절차 개선… FTA 활용 지원 확대&amp;nbsp;&amp;nbsp;한국관세신문</t>
+          <t>염소고기 원산지 'DNA·동위원소'로 판별한다&amp;nbsp;&amp;nbsp;세이프타임즈</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Mon, 08 Jun 2026 09:06:58 GMT</t>
+          <t>Mon, 08 Jun 2026 04:26:46 GMT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE12bjhncGV5d2daM0k2V18ySGJ0RjFUUmxzS1dkM2x6UGtTQzROSTdtcGRhZndJdjhodFRkTi1tVFdxbkU5MFhBbHphdG4xNTdxSlJxTUZpbkZmVFJ4UDc4NGtCOTVzTlZGWndF0gFrQVVfeXFMTXZuOGdwZXl3Z1ozSTZXXzJIYnRGMVRSbHNLV2QzbHpQa1NDNE5JN21wZGFmd0l2OGh0VGROLW1UV3FuRTkwWEFsemF0bjE1N3FKUnFNRmluRmZUUnhQNzg0a0I5NXNOVkZad0U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE5sM1l1aWpYeWpYVWw3a01weWdjaTZrVVYxOUVJUkNZT2ctX1lSb0hydWExVnJTMk5BS1o0bWZpWXJGd0FXRDVZR2JLc21fQUp4d1BtUDZQTGtuMFRCQWFKZ3htVm45cnZaSFVNTzhMYjgyZnfSAXNBVV95cUxObDNZdWlqWHlqWFVsN2tNcHlnY2k2a1VWMTlFSVJDWU9nLV9ZUm9IcnVhMVZyUzJOQUtaNG1maVlyRndBV0Q1WUdiS3NtX0FKeHdQbVA2UExrbjBUQkFhSmd4bVZuOXJ2WkhVTU84TGI4MmZ3?oc=5</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I32" t="inlineStr"/>
     </row>
@@ -1618,22 +1618,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>염소고기 원산지 'DNA·동위원소'로 판별한다 - 세이프타임즈</t>
+          <t>우유 원산지 표시제 확대 논의...카페·베이커리도 포함되나 - 전자신문</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>염소고기 원산지 'DNA·동위원소'로 판별한다&amp;nbsp;&amp;nbsp;세이프타임즈</t>
+          <t>우유 원산지 표시제 확대 논의...카페·베이커리도 포함되나&amp;nbsp;&amp;nbsp;전자신문</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Mon, 08 Jun 2026 04:26:46 GMT</t>
+          <t>Mon, 08 Jun 2026 04:48:56 GMT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE5sM1l1aWpYeWpYVWw3a01weWdjaTZrVVYxOUVJUkNZT2ctX1lSb0hydWExVnJTMk5BS1o0bWZpWXJGd0FXRDVZR2JLc21fQUp4d1BtUDZQTGtuMFRCQWFKZ3htVm45cnZaSFVNTzhMYjgyZnfSAXNBVV95cUxObDNZdWlqWHlqWFVsN2tNcHlnY2k2a1VWMTlFSVJDWU9nLV9ZUm9IcnVhMVZyUzJOQUtaNG1maVlyRndBV0Q1WUdiS3NtX0FKeHdQbVA2UExrbjBUQkFhSmd4bVZuOXJ2WkhVTU84TGI4MmZ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiTkFVX3lxTFB5eEctUlBMZHdXcEJRRHNmQ3dDYmZKV2gtbHNVQS1RanlRVEFUa0U0QTZpVDF2SjhmVElrZXRhLXZLMzNjc3VzWGdRNFZ2dw?oc=5</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1655,22 +1655,22 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>우유 원산지 표시제 확대 논의...카페·베이커리도 포함되나 - 전자신문</t>
+          <t>염소고기 원산지 논란 끝낸다…농관원, 판별기술 확보 - 식약일보</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>우유 원산지 표시제 확대 논의...카페·베이커리도 포함되나&amp;nbsp;&amp;nbsp;전자신문</t>
+          <t>염소고기 원산지 논란 끝낸다…농관원, 판별기술 확보&amp;nbsp;&amp;nbsp;식약일보</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Mon, 08 Jun 2026 04:48:56 GMT</t>
+          <t>Mon, 08 Jun 2026 07:21:00 GMT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiTkFVX3lxTFB5eEctUlBMZHdXcEJRRHNmQ3dDYmZKV2gtbHNVQS1RanlRVEFUa0U0QTZpVDF2SjhmVElrZXRhLXZLMzNjc3VzWGdRNFZ2dw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiO0FVX3lxTE5DZDlodndIZGdfa1B1ODJVMkdGZGFYT2hfRHpvQkZuVVp1MjZWRlI4dzlkS3B5WWdfUkpj?oc=5</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1692,22 +1692,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>염소고기 원산지 논란 끝낸다…농관원, 판별기술 확보 - 식약일보</t>
+          <t>'국내산 둔갑' 염소고기 꼼짝마…정확도 95% ‘원산지 판별법’ 개발 - 전민일보</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>염소고기 원산지 논란 끝낸다…농관원, 판별기술 확보&amp;nbsp;&amp;nbsp;식약일보</t>
+          <t>'국내산 둔갑' 염소고기 꼼짝마…정확도 95% ‘원산지 판별법’ 개발&amp;nbsp;&amp;nbsp;전민일보</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Mon, 08 Jun 2026 07:21:00 GMT</t>
+          <t>Mon, 08 Jun 2026 06:46:46 GMT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiO0FVX3lxTE5DZDlodndIZGdfa1B1ODJVMkdGZGFYT2hfRHpvQkZuVVp1MjZWRlI4dzlkS3B5WWdfUkpj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE5GaVRIMmwzbURmbVlLMjhQWk83RzcxM0xXM2pDV0tWdUJQQzA3QmJobUVPQ3prX1ZGdEhlV0RfOVNNdkZJU0JocVF2Z1hyRUtKWld4VEozQVFlR2NOVUtIbzVZWUlHdw?oc=5</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1729,22 +1729,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>'국내산 둔갑' 염소고기 꼼짝마…정확도 95% ‘원산지 판별법’ 개발 - 전민일보</t>
+          <t>농관원, 국내 첫 염소고기 원산지 판별기술 개발...95% 이상 구분 - 푸드투데이</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>'국내산 둔갑' 염소고기 꼼짝마…정확도 95% ‘원산지 판별법’ 개발&amp;nbsp;&amp;nbsp;전민일보</t>
+          <t>농관원, 국내 첫 염소고기 원산지 판별기술 개발...95% 이상 구분&amp;nbsp;&amp;nbsp;푸드투데이</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Mon, 08 Jun 2026 06:46:46 GMT</t>
+          <t>Mon, 08 Jun 2026 01:34:43 GMT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE5GaVRIMmwzbURmbVlLMjhQWk83RzcxM0xXM2pDV0tWdUJQQzA3QmJobUVPQ3prX1ZGdEhlV0RfOVNNdkZJU0JocVF2Z1hyRUtKWld4VEozQVFlR2NOVUtIbzVZWUlHdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE5CWFptbzRiY09WV1BOSGhVbFJkZ2J0WkxzTUpSZW5FOUp6WG1IUHpPdUVkVy05WUVOcnA1U3ZJQkxQblMzT2lhaGoxdGFkVk1ncVBUamduVHZlVXV4Mkp1VQ?oc=5</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1988,22 +1988,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>中 수출통제에…中희토류 日수입량 80%가량 급감 - 네이트</t>
+          <t>中, 대일 희토류 수출 80%↓…日, 호주·인도 등 대안 모색 - 이데일리</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>中 수출통제에…中희토류 日수입량 80%가량 급감&amp;nbsp;&amp;nbsp;네이트</t>
+          <t>中, 대일 희토류 수출 80%↓…日, 호주·인도 등 대안 모색&amp;nbsp;&amp;nbsp;이데일리</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Mon, 08 Jun 2026 04:00:00 GMT</t>
+          <t>Mon, 08 Jun 2026 00:47:13 GMT</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTFB6czNPRHJYZ0lOcEF5dGxSYW9DbHB5TjVHVEQ4WTVMZ082VE82Y0djelhvVlR4SnMtX3M2YU5iYmVnX0R1MXNKNjRCUFhmWmhZTGRF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNNVpyUlJMaXFIaE43RHJUdHhOcVd4d3oyYUlnOW1KM2VZeXB1MXg4aUlqUjFpV2ZSR1BDcTE2T0VabEVnSGlpY216MkNwTl9CTXRPR3k3WC02R19qNENTZmhvMU1FZnJxaWg0UWxuUVJmWU1MRk5tbzdQSFNSTXpmaw?oc=5</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2013,34 +2013,34 @@
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>수출통제</t>
+          <t>무역구제</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>中 수출통제에…中희토류 日수입량 80%가량 급감 - MSN</t>
+          <t>가스안전公 신임 부사장에 조영원 前울산자유무역지역관리원장 - 국토일보</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>中 수출통제에…中희토류 日수입량 80%가량 급감&amp;nbsp;&amp;nbsp;MSN</t>
+          <t>가스안전公 신임 부사장에 조영원 前울산자유무역지역관리원장&amp;nbsp;&amp;nbsp;국토일보</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Mon, 08 Jun 2026 08:57:09 GMT</t>
+          <t>Mon, 08 Jun 2026 09:05:00 GMT</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAJBVV95cUxNV3JqajBrNEpodFRmWi1KeWZsRDU0QnZrQ19hbHJzNko5TnB0NWR0LW1GdlpUb05Ka183NXFLeFN6S0NseU56d2U3MkdneEZlWnNrZlNkOUVPS2VBSUZWQlljNF8xVVBSWjQ4cDJ1NjFQclktS0paUTY4UjJyanZpczVhVjFKZDE3ems1R1BwMjd4V1JyOF9KdEpCWHlqbzdhNjFYUGVyZU9aTmVKQzRieDlpY0owUDhrZEVYMnJRSnBVRUZReGdzd01jNlRkTUdqZG9yTTVYOFJXbVBLSnB0QldCMTVfZzVLS3NxYWEwNE9WTTVTZWUwaGFzd3pzMkg5UWJhUUsyYjRSZmMxckdSS3Zmc3ljb3JnWGRScmFJZGllWEpzTzFiQVVCSlV5VHJwVGpyUlhfSlRseGZ6TjRtUXkwWDE0aHRY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE85N1BBZmhpdE9GN3M4SjRuU3NxZGVpejhvRzZwR3hoSVphbDJJZjFIU2VEc25XQlI4VUJlS3NQT3F4dHdvUlZUSlRFRjRLaUVmb1VUdEpQT1R1a2c1a1hvVllsYkc?oc=5</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2057,27 +2057,27 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>수출통제</t>
+          <t>무역구제</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>中, 대일 희토류 수출 80%↓…日, 호주·인도 등 대안 모색 - 이데일리</t>
+          <t>가스안전공사 부사장에 조영원 전 울산자유무역지역관리원장 - 네이트</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>中, 대일 희토류 수출 80%↓…日, 호주·인도 등 대안 모색&amp;nbsp;&amp;nbsp;이데일리</t>
+          <t>가스안전공사 부사장에 조영원 전 울산자유무역지역관리원장&amp;nbsp;&amp;nbsp;네이트</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Mon, 08 Jun 2026 00:47:13 GMT</t>
+          <t>Mon, 08 Jun 2026 09:10:00 GMT</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxNNVpyUlJMaXFIaE43RHJUdHhOcVd4d3oyYUlnOW1KM2VZeXB1MXg4aUlqUjFpV2ZSR1BDcTE2T0VabEVnSGlpY216MkNwTl9CTXRPR3k3WC02R19qNENTZmhvMU1FZnJxaWg0UWxuUVJmWU1MRk5tbzdQSFNSTXpmaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE0zZzN1RUpxaFVwUUJvMFRZSGdpTEhEMFRoVUw0bmZDc2FIRUo1aHhZS3lHTmtqcmJ6N1RlcEdQMzBkN3kzVW95WVJsRFE3a0NGMjZj?oc=5</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2087,83 +2087,9 @@
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>무역구제</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>가스안전公 신임 부사장에 조영원 前울산자유무역지역관리원장 - 국토일보</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>가스안전公 신임 부사장에 조영원 前울산자유무역지역관리원장&amp;nbsp;&amp;nbsp;국토일보</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Mon, 08 Jun 2026 09:05:00 GMT</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE85N1BBZmhpdE9GN3M4SjRuU3NxZGVpejhvRzZwR3hoSVphbDJJZjFIU2VEc25XQlI4VUJlS3NQT3F4dHdvUlZUSlRFRjRLaUVmb1VUdEpQT1R1a2c1a1hvVllsYkc?oc=5</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="n">
-        <v>1</v>
-      </c>
-      <c r="I46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>무역구제</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>가스안전공사 부사장에 조영원 전 울산자유무역지역관리원장 - 네이트</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>가스안전공사 부사장에 조영원 전 울산자유무역지역관리원장&amp;nbsp;&amp;nbsp;네이트</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Mon, 08 Jun 2026 09:10:00 GMT</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE0zZzN1RUpxaFVwUUJvMFRZSGdpTEhEMFRoVUw0bmZDc2FIRUo1aHhZS3lHTmtqcmJ6N1RlcEdQMzBkN3kzVW95WVJsRFE3a0NGMjZj?oc=5</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="n">
-        <v>1</v>
-      </c>
-      <c r="I47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
